--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7362,7 +7362,7 @@
         <v>136352545</v>
       </c>
       <c r="B59" t="n">
-        <v>106517</v>
+        <v>106520</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136352621</v>
       </c>
       <c r="B60" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>136352540</v>
       </c>
       <c r="B61" t="n">
-        <v>98207</v>
+        <v>98210</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>136352542</v>
       </c>
       <c r="B62" t="n">
-        <v>98393</v>
+        <v>98396</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7362,7 +7362,7 @@
         <v>136352545</v>
       </c>
       <c r="B59" t="n">
-        <v>106520</v>
+        <v>106521</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136352621</v>
       </c>
       <c r="B60" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>136352540</v>
       </c>
       <c r="B61" t="n">
-        <v>98210</v>
+        <v>98211</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>136352542</v>
       </c>
       <c r="B62" t="n">
-        <v>98396</v>
+        <v>98397</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7362,7 +7362,7 @@
         <v>136352545</v>
       </c>
       <c r="B59" t="n">
-        <v>106521</v>
+        <v>106526</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136352621</v>
       </c>
       <c r="B60" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>136352540</v>
       </c>
       <c r="B61" t="n">
-        <v>98211</v>
+        <v>98216</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>136352542</v>
       </c>
       <c r="B62" t="n">
-        <v>98397</v>
+        <v>98402</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>136352484</v>
       </c>
       <c r="B63" t="n">
-        <v>57196</v>
+        <v>57198</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ111"/>
+  <dimension ref="A1:AZ112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7362,7 +7362,7 @@
         <v>136352545</v>
       </c>
       <c r="B59" t="n">
-        <v>106526</v>
+        <v>106528</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136352621</v>
       </c>
       <c r="B60" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>136352540</v>
       </c>
       <c r="B61" t="n">
-        <v>98216</v>
+        <v>98218</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>136352542</v>
       </c>
       <c r="B62" t="n">
-        <v>98402</v>
+        <v>98404</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8161,10 +8161,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>72870974</v>
+        <v>136864192</v>
       </c>
       <c r="B66" t="n">
-        <v>99038</v>
+        <v>104073</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8172,33 +8172,41 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>223597</v>
+        <v>223284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Skräddarnas, Vstm</t>
+          <t>Övre Gillermossen, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>517322</v>
+        <v>517293</v>
       </c>
       <c r="R66" t="n">
-        <v>6632880</v>
+        <v>6632960</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8222,12 +8230,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8236,39 +8244,41 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Dike</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>grusvägsdike i barrskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72870974</t>
+          <t>https://artportalen.se/Sighting/136864192</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>72870975</v>
+        <v>72870974</v>
       </c>
       <c r="B67" t="n">
         <v>99038</v>
@@ -8299,10 +8309,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>517560</v>
+        <v>517322</v>
       </c>
       <c r="R67" t="n">
-        <v>6632442</v>
+        <v>6632880</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8369,62 +8379,47 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72870975</t>
+          <t>https://artportalen.se/Sighting/72870974</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>80252484</v>
+        <v>72870975</v>
       </c>
       <c r="B68" t="n">
-        <v>93197</v>
+        <v>99038</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>223597</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Treöresvägen, Vstm</t>
+          <t>Skräddarnas, Vstm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>520297</v>
+        <v>517560</v>
       </c>
       <c r="R68" t="n">
-        <v>6632071</v>
+        <v>6632442</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8451,12 +8446,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8465,31 +8460,39 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80252484</t>
+          <t>https://artportalen.se/Sighting/72870975</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>80252535</v>
+        <v>80252484</v>
       </c>
       <c r="B69" t="n">
         <v>93197</v>
@@ -8519,7 +8522,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8535,10 +8538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520387</v>
+        <v>520297</v>
       </c>
       <c r="R69" t="n">
-        <v>6631778</v>
+        <v>6632071</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8597,42 +8600,50 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80252535</t>
+          <t>https://artportalen.se/Sighting/80252484</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>80252435</v>
+        <v>80252535</v>
       </c>
       <c r="B70" t="n">
-        <v>91872</v>
+        <v>93197</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -8641,13 +8652,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520323</v>
+        <v>520387</v>
       </c>
       <c r="R70" t="n">
-        <v>6631763</v>
+        <v>6631778</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8703,16 +8714,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80252435</t>
+          <t>https://artportalen.se/Sighting/80252535</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>85567007</v>
+        <v>80252435</v>
       </c>
       <c r="B71" t="n">
-        <v>57141</v>
+        <v>91872</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8720,45 +8731,40 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kloten, Vstm</t>
+          <t>Treöresvägen, Vstm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520354</v>
+        <v>520323</v>
       </c>
       <c r="R71" t="n">
-        <v>6631282</v>
+        <v>6631763</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8782,12 +8788,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2020-04-15</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2020-04-15</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8796,33 +8802,34 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85567007</t>
+          <t>https://artportalen.se/Sighting/80252435</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122660696</v>
+        <v>85567007</v>
       </c>
       <c r="B72" t="n">
-        <v>56766</v>
+        <v>57141</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8830,47 +8837,45 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100077</v>
+        <v>100138</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Nyckelbäcken, Vstm</t>
+          <t>Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519239</v>
+        <v>520354</v>
       </c>
       <c r="R72" t="n">
-        <v>6629256</v>
+        <v>6631282</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8894,17 +8899,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2019-08-21</t>
+          <t>2020-04-15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2019-08-21</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Vägtrumma</t>
+          <t>2020-04-15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8915,36 +8915,31 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AS72" t="inlineStr">
-        <is>
-          <t>Per Ingvarsson</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Via Henrik Josefsson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122660696</t>
+          <t>https://artportalen.se/Sighting/85567007</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>93696874</v>
+        <v>122660696</v>
       </c>
       <c r="B73" t="n">
-        <v>57141</v>
+        <v>56766</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8952,56 +8947,47 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100138</v>
+        <v>100077</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>Nyckelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>522428</v>
+        <v>519239</v>
       </c>
       <c r="R73" t="n">
-        <v>6628384</v>
+        <v>6629256</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9025,22 +9011,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2019-08-21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2019-08-21</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Vägtrumma</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9051,31 +9032,36 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>Per Ingvarsson</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bengt-Ove Lindberg</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bengt-Ove Lindberg</t>
+          <t>Via Henrik Josefsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93696874</t>
+          <t>https://artportalen.se/Sighting/122660696</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>92859293</v>
+        <v>93696874</v>
       </c>
       <c r="B74" t="n">
-        <v>57144</v>
+        <v>57141</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9083,29 +9069,41 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102613</v>
+        <v>100138</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -9114,13 +9112,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>522606</v>
+        <v>522428</v>
       </c>
       <c r="R74" t="n">
-        <v>6628180</v>
+        <v>6628384</v>
       </c>
       <c r="S74" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9144,22 +9142,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9185,73 +9183,61 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92859293</t>
+          <t>https://artportalen.se/Sighting/93696874</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>98536837</v>
+        <v>92859293</v>
       </c>
       <c r="B75" t="n">
-        <v>56816</v>
+        <v>57144</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>205998</v>
+        <v>102613</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norrmogen, Vstm</t>
+          <t>Lindesberg, Vstm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>522653</v>
+        <v>522606</v>
       </c>
       <c r="R75" t="n">
-        <v>6628363</v>
+        <v>6628180</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9275,22 +9261,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>00:47</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>00:47</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9305,24 +9291,24 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Bengt-Ove Lindberg</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Bengt-Ove Lindberg</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536837</t>
+          <t>https://artportalen.se/Sighting/92859293</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>98536839</v>
+        <v>98536837</v>
       </c>
       <c r="B76" t="n">
         <v>56816</v>
@@ -9376,10 +9362,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>522680</v>
+        <v>522653</v>
       </c>
       <c r="R76" t="n">
-        <v>6628361</v>
+        <v>6628363</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9447,13 +9433,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536839</t>
+          <t>https://artportalen.se/Sighting/98536837</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>98536862</v>
+        <v>98536839</v>
       </c>
       <c r="B77" t="n">
         <v>56816</v>
@@ -9507,10 +9493,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>522163</v>
+        <v>522680</v>
       </c>
       <c r="R77" t="n">
-        <v>6628351</v>
+        <v>6628361</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9537,22 +9523,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>23:46</t>
+          <t>00:47</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-07-25</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>23:46</t>
+          <t>00:47</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9578,13 +9564,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536862</t>
+          <t>https://artportalen.se/Sighting/98536839</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>98536863</v>
+        <v>98536862</v>
       </c>
       <c r="B78" t="n">
         <v>56816</v>
@@ -9638,10 +9624,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>522878</v>
+        <v>522163</v>
       </c>
       <c r="R78" t="n">
-        <v>6628396</v>
+        <v>6628351</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9673,7 +9659,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>23:44</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9683,7 +9669,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>23:44</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9709,13 +9695,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536863</t>
+          <t>https://artportalen.se/Sighting/98536862</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>98536882</v>
+        <v>98536863</v>
       </c>
       <c r="B79" t="n">
         <v>56816</v>
@@ -9769,10 +9755,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>522384</v>
+        <v>522878</v>
       </c>
       <c r="R79" t="n">
-        <v>6628361</v>
+        <v>6628396</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9799,22 +9785,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
+          <t>2021-07-23</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>23:44</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>23:44</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9840,13 +9826,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536882</t>
+          <t>https://artportalen.se/Sighting/98536863</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>98536883</v>
+        <v>98536882</v>
       </c>
       <c r="B80" t="n">
         <v>56816</v>
@@ -9900,7 +9886,7 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>522735</v>
+        <v>522384</v>
       </c>
       <c r="R80" t="n">
         <v>6628361</v>
@@ -9935,7 +9921,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>23:55</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9945,7 +9931,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>23:55</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9971,13 +9957,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536883</t>
+          <t>https://artportalen.se/Sighting/98536882</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>98536884</v>
+        <v>98536883</v>
       </c>
       <c r="B81" t="n">
         <v>56816</v>
@@ -10031,10 +10017,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>522777</v>
+        <v>522735</v>
       </c>
       <c r="R81" t="n">
-        <v>6628381</v>
+        <v>6628361</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10066,7 +10052,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10076,7 +10062,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10102,13 +10088,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536884</t>
+          <t>https://artportalen.se/Sighting/98536883</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>98536885</v>
+        <v>98536884</v>
       </c>
       <c r="B82" t="n">
         <v>56816</v>
@@ -10162,10 +10148,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>522788</v>
+        <v>522777</v>
       </c>
       <c r="R82" t="n">
-        <v>6628388</v>
+        <v>6628381</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10233,13 +10219,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536885</t>
+          <t>https://artportalen.se/Sighting/98536884</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>98536886</v>
+        <v>98536885</v>
       </c>
       <c r="B83" t="n">
         <v>56816</v>
@@ -10293,10 +10279,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>522804</v>
+        <v>522788</v>
       </c>
       <c r="R83" t="n">
-        <v>6628394</v>
+        <v>6628388</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10364,16 +10350,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536886</t>
+          <t>https://artportalen.se/Sighting/98536885</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>95457108</v>
+        <v>98536886</v>
       </c>
       <c r="B84" t="n">
-        <v>93215</v>
+        <v>56816</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10381,40 +10367,56 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4368</v>
+        <v>205998</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Ormpussen, Vstm</t>
+          <t>Norrmogen, Vstm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523487</v>
+        <v>522804</v>
       </c>
       <c r="R84" t="n">
-        <v>6628132</v>
+        <v>6628394</v>
       </c>
       <c r="S84" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10438,12 +10440,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2021-07-21</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10452,72 +10464,74 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95457108</t>
+          <t>https://artportalen.se/Sighting/98536886</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>98351190</v>
+        <v>95457108</v>
       </c>
       <c r="B85" t="n">
-        <v>97986</v>
+        <v>93215</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221946</v>
+        <v>4368</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gammelbo, Vstm</t>
+          <t>Ormpussen, Vstm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523565</v>
+        <v>523487</v>
       </c>
       <c r="R85" t="n">
-        <v>6627791</v>
+        <v>6628132</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10541,12 +10555,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10555,94 +10569,72 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr">
-        <is>
-          <t>Miniforskningsresan Extensus Örebro län 2021</t>
-        </is>
-      </c>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98351190</t>
+          <t>https://artportalen.se/Sighting/95457108</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>98536876</v>
+        <v>98351190</v>
       </c>
       <c r="B86" t="n">
-        <v>56816</v>
+        <v>97986</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>205998</v>
+        <v>221946</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrmogen, Vstm</t>
+          <t>Gammelbo, Vstm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>525086</v>
+        <v>523565</v>
       </c>
       <c r="R86" t="n">
-        <v>6628007</v>
+        <v>6627791</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10666,22 +10658,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>00:16</t>
+          <t>2021-05-08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>00:16</t>
+          <t>2021-05-08</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10696,27 +10678,31 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536876</t>
+          <t>https://artportalen.se/Sighting/98351190</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>98537195</v>
+        <v>98536876</v>
       </c>
       <c r="B87" t="n">
-        <v>56814</v>
+        <v>56816</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10724,21 +10710,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100015</v>
+        <v>205998</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -10758,7 +10744,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10767,10 +10753,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>525810</v>
+        <v>525086</v>
       </c>
       <c r="R87" t="n">
-        <v>6627350</v>
+        <v>6628007</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10797,22 +10783,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>00:16</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
           <t>2021-07-23</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10823,11 +10809,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AS87" t="inlineStr">
-        <is>
-          <t>Johnny de Jong</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10843,43 +10824,43 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98537195</t>
+          <t>https://artportalen.se/Sighting/98536876</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>98536579</v>
+        <v>98537195</v>
       </c>
       <c r="B88" t="n">
-        <v>56823</v>
+        <v>56814</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>205992</v>
+        <v>100015</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10979,43 +10960,43 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536579</t>
+          <t>https://artportalen.se/Sighting/98537195</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>98536910</v>
+        <v>98536579</v>
       </c>
       <c r="B89" t="n">
-        <v>56816</v>
+        <v>56823</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11115,16 +11096,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536910</t>
+          <t>https://artportalen.se/Sighting/98536579</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>98535806</v>
+        <v>98536910</v>
       </c>
       <c r="B90" t="n">
-        <v>56837</v>
+        <v>56816</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11132,26 +11113,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11251,16 +11232,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98535806</t>
+          <t>https://artportalen.se/Sighting/98536910</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124825217</v>
+        <v>98535806</v>
       </c>
       <c r="B91" t="n">
-        <v>93197</v>
+        <v>56837</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11268,38 +11249,53 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>206002</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Norrmogen, Vstm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>498767</v>
+        <v>525810</v>
       </c>
       <c r="R91" t="n">
-        <v>6626190</v>
+        <v>6627350</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -11321,22 +11317,27 @@
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Ramsberg</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11347,28 +11348,33 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>Johnny de Jong</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825217</t>
+          <t>https://artportalen.se/Sighting/98535806</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124825221</v>
+        <v>124825217</v>
       </c>
       <c r="B92" t="n">
         <v>93197</v>
@@ -11407,10 +11413,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>498811</v>
+        <v>498767</v>
       </c>
       <c r="R92" t="n">
-        <v>6626221</v>
+        <v>6626190</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -11473,59 +11479,55 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825221</t>
+          <t>https://artportalen.se/Sighting/124825217</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124825220</v>
+        <v>124825221</v>
       </c>
       <c r="B93" t="n">
-        <v>57141</v>
+        <v>93197</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>498810</v>
+        <v>498811</v>
       </c>
       <c r="R93" t="n">
-        <v>6626227</v>
+        <v>6626221</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11588,13 +11590,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825220</t>
+          <t>https://artportalen.se/Sighting/124825221</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124825285</v>
+        <v>124825220</v>
       </c>
       <c r="B94" t="n">
         <v>57141</v>
@@ -11628,30 +11630,22 @@
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>498809</v>
+        <v>498810</v>
       </c>
       <c r="R94" t="n">
-        <v>6626228</v>
+        <v>6626227</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11685,7 +11679,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.Synobs. Tupp</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11711,16 +11705,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825285</t>
+          <t>https://artportalen.se/Sighting/124825220</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124825211</v>
+        <v>124825285</v>
       </c>
       <c r="B95" t="n">
-        <v>5179</v>
+        <v>57141</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11728,21 +11722,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -11750,19 +11744,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>498899</v>
+        <v>498809</v>
       </c>
       <c r="R95" t="n">
-        <v>6625787</v>
+        <v>6626228</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11796,7 +11802,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.Synobs. Tupp</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11822,13 +11828,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825211</t>
+          <t>https://artportalen.se/Sighting/124825285</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124825214</v>
+        <v>124825211</v>
       </c>
       <c r="B96" t="n">
         <v>5179</v>
@@ -11858,7 +11864,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11867,10 +11873,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>499066</v>
+        <v>498899</v>
       </c>
       <c r="R96" t="n">
-        <v>6626115</v>
+        <v>6625787</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11933,13 +11939,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825214</t>
+          <t>https://artportalen.se/Sighting/124825211</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124825290</v>
+        <v>124825214</v>
       </c>
       <c r="B97" t="n">
         <v>5179</v>
@@ -11969,7 +11975,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11978,13 +11984,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>498898</v>
+        <v>499066</v>
       </c>
       <c r="R97" t="n">
-        <v>6625781</v>
+        <v>6626115</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12044,16 +12050,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825290</t>
+          <t>https://artportalen.se/Sighting/124825214</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124825216</v>
+        <v>124825290</v>
       </c>
       <c r="B98" t="n">
-        <v>99035</v>
+        <v>5179</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12061,21 +12067,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219790</v>
+        <v>100526</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12089,13 +12095,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>498747</v>
+        <v>498898</v>
       </c>
       <c r="R98" t="n">
-        <v>6625877</v>
+        <v>6625781</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12155,16 +12161,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825216</t>
+          <t>https://artportalen.se/Sighting/124825290</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>66418932</v>
+        <v>124825216</v>
       </c>
       <c r="B99" t="n">
-        <v>99036</v>
+        <v>99035</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12172,44 +12178,41 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>223591</v>
+        <v>219790</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Strävtorp, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>496339</v>
+        <v>498747</v>
       </c>
       <c r="R99" t="n">
-        <v>6624902</v>
+        <v>6625877</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12233,22 +12236,17 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2017-06-23</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2017-06-23</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12263,62 +12261,69 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Bengt Adamsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Bengt Adamsson , Bodil Nyström, Conny Palm, Stig Carlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66418932</t>
+          <t>https://artportalen.se/Sighting/124825216</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>122230880</v>
+        <v>66418932</v>
       </c>
       <c r="B100" t="n">
-        <v>79327</v>
+        <v>99036</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>223591</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Rasbacktjärn, Vstm</t>
+          <t>Strävtorp, Vstm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>495350</v>
+        <v>496339</v>
       </c>
       <c r="R100" t="n">
-        <v>6624698</v>
+        <v>6624902</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -12345,12 +12350,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2017-06-23</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2017-06-23</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12365,44 +12380,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Bengt Adamsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Bengt Adamsson , Bodil Nyström, Conny Palm, Stig Carlsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122230880</t>
+          <t>https://artportalen.se/Sighting/66418932</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122230857</v>
+        <v>122230880</v>
       </c>
       <c r="B101" t="n">
-        <v>80467</v>
+        <v>79327</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -12417,10 +12432,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>495356</v>
+        <v>495350</v>
       </c>
       <c r="R101" t="n">
-        <v>6624327</v>
+        <v>6624698</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -12447,12 +12462,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12478,16 +12493,16 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122230857</t>
+          <t>https://artportalen.se/Sighting/122230880</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122230848</v>
+        <v>122230857</v>
       </c>
       <c r="B102" t="n">
-        <v>57141</v>
+        <v>80467</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12495,42 +12510,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100138</v>
+        <v>6463</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rasbacktjärn, Vstm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>495309</v>
+        <v>495356</v>
       </c>
       <c r="R102" t="n">
-        <v>6624438</v>
+        <v>6624327</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12588,55 +12595,59 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122230848</t>
+          <t>https://artportalen.se/Sighting/122230857</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122230856</v>
+        <v>122230848</v>
       </c>
       <c r="B103" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rasbacktjärn, Vstm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>495359</v>
+        <v>495309</v>
       </c>
       <c r="R103" t="n">
-        <v>6624369</v>
+        <v>6624438</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12694,51 +12705,55 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122230856</t>
+          <t>https://artportalen.se/Sighting/122230848</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>82883664</v>
+        <v>122230856</v>
       </c>
       <c r="B104" t="n">
-        <v>96554</v>
+        <v>58114</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>210</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Hammarskogsån, Vstm</t>
+          <t>Rasbacktjärn, Vstm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>503753</v>
+        <v>495359</v>
       </c>
       <c r="R104" t="n">
-        <v>6624241</v>
+        <v>6624369</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12765,12 +12780,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12781,45 +12796,31 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>Barrskog i litet dalstråk</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883664</t>
+          <t>https://artportalen.se/Sighting/122230856</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>82883685</v>
+        <v>82883664</v>
       </c>
       <c r="B105" t="n">
-        <v>97989</v>
+        <v>96554</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12827,21 +12828,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221941</v>
+        <v>210</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12851,10 +12852,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>504568</v>
+        <v>503753</v>
       </c>
       <c r="R105" t="n">
-        <v>6623836</v>
+        <v>6624241</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12900,7 +12901,12 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>Tallbestånd</t>
+          <t>Barrskog i litet dalstråk</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12921,16 +12927,16 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883685</t>
+          <t>https://artportalen.se/Sighting/82883664</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135456621</v>
+        <v>82883685</v>
       </c>
       <c r="B106" t="n">
-        <v>57783</v>
+        <v>97989</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12938,49 +12944,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>102118</v>
+        <v>221941</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Midtjärnsviken, Vstm</t>
+          <t>Hammarskogsån, Vstm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>500203</v>
+        <v>504568</v>
       </c>
       <c r="R106" t="n">
-        <v>6623603</v>
+        <v>6623836</v>
       </c>
       <c r="S106" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13004,27 +12998,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>22:35</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>22:42</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Även lockläte hörs några ggr.</t>
+          <t>2018-10-03</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13035,31 +13014,40 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Tallbestånd</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Fredrik Johansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Fredrik Johansson</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135456621</t>
+          <t>https://artportalen.se/Sighting/82883685</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>82883645</v>
+        <v>135456621</v>
       </c>
       <c r="B107" t="n">
-        <v>97678</v>
+        <v>57783</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13067,37 +13055,49 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2326</v>
+        <v>102118</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Nees</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Hammarskogsån, Vstm</t>
+          <t>Midtjärnsviken, Vstm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>503428</v>
+        <v>500203</v>
       </c>
       <c r="R107" t="n">
-        <v>6623052</v>
+        <v>6623603</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13121,12 +13121,27 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>22:42</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Även lockläte hörs några ggr.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13137,45 +13152,31 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>Sumpdråg</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Murken ved av lövträd</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Fredrik Johansson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Fredrik Johansson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883645</t>
+          <t>https://artportalen.se/Sighting/135456621</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>82883638</v>
+        <v>82883645</v>
       </c>
       <c r="B108" t="n">
-        <v>97780</v>
+        <v>97678</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13183,21 +13184,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2389</v>
+        <v>2326</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13207,10 +13208,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>503461</v>
+        <v>503428</v>
       </c>
       <c r="R108" t="n">
-        <v>6623044</v>
+        <v>6623052</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -13256,12 +13257,12 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Sumpdråg</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>Blocksida</t>
+          <t>Murken ved av lövträd</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13282,16 +13283,16 @@
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883638</t>
+          <t>https://artportalen.se/Sighting/82883645</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>82883606</v>
+        <v>82883638</v>
       </c>
       <c r="B109" t="n">
-        <v>97231</v>
+        <v>97780</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13299,21 +13300,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2869</v>
+        <v>2389</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13323,10 +13324,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>503469</v>
+        <v>503461</v>
       </c>
       <c r="R109" t="n">
-        <v>6623043</v>
+        <v>6623044</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -13375,6 +13376,11 @@
           <t>Barrsumpskog</t>
         </is>
       </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Blocksida</t>
+        </is>
+      </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
@@ -13393,38 +13399,38 @@
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883606</t>
+          <t>https://artportalen.se/Sighting/82883638</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>82883551</v>
+        <v>82883606</v>
       </c>
       <c r="B110" t="n">
-        <v>93215</v>
+        <v>97231</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4368</v>
+        <v>2869</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13434,10 +13440,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>501532</v>
+        <v>503469</v>
       </c>
       <c r="R110" t="n">
-        <v>6622785</v>
+        <v>6623043</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -13483,7 +13489,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Örtgranskog vid å</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -13504,13 +13510,13 @@
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883551</t>
+          <t>https://artportalen.se/Sighting/82883606</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>89825681</v>
+        <v>82883551</v>
       </c>
       <c r="B111" t="n">
         <v>93215</v>
@@ -13541,17 +13547,17 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Hammarbäcken, Vstm</t>
+          <t>Hammarskogsån, Vstm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>501528</v>
+        <v>501532</v>
       </c>
       <c r="R111" t="n">
-        <v>6622791</v>
+        <v>6622785</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13575,12 +13581,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2018-10-03</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13594,31 +13600,142 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>Åstrand med lövrik blandskog</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Äldre granbestånd</t>
+          <t>Örtgranskog vid å</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883551</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>89825681</v>
+      </c>
+      <c r="B112" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Hammarbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>501528</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6622791</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2020-10-22</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2020-10-22</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Åstrand med lövrik blandskog</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Äldre granbestånd</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
           <t>Henrik Weibull</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
+      <c r="AX112" t="inlineStr">
         <is>
           <t>Henrik Weibull</t>
         </is>
       </c>
-      <c r="AY111" t="inlineStr">
+      <c r="AY112" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
+      <c r="AZ112" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89825681</t>
         </is>
@@ -13736,6 +13853,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ112"/>
+  <dimension ref="A1:AZ114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7812,10 +7812,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136352484</v>
+        <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>57198</v>
+        <v>111332</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7823,58 +7823,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102613</v>
+        <v>220240</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Södra Kloten, N om, Vstm</t>
+          <t>Klotsboda S om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>516955</v>
+        <v>516786</v>
       </c>
       <c r="R63" t="n">
-        <v>6634420</v>
+        <v>6635274</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7901,17 +7885,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Flög in över vägen framför bilen och blev nästan påkörd.</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7920,12 +7899,13 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Lingontallskog</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7939,19 +7919,23 @@
           <t>Michael Andersson</t>
         </is>
       </c>
-      <c r="AY63" t="inlineStr"/>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136352484</t>
+          <t>https://artportalen.se/Sighting/136941249</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>72870976</v>
+        <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>97986</v>
+        <v>106528</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7959,16 +7943,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221946</v>
+        <v>221157</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7977,19 +7961,23 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>S Kloten, Vstm</t>
+          <t>Klotsboda SSO om, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>516944</v>
+        <v>516782</v>
       </c>
       <c r="R64" t="n">
-        <v>6634445</v>
+        <v>6635311</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8013,12 +8001,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8027,80 +8015,105 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72870976</t>
+          <t>https://artportalen.se/Sighting/136941079</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>85567146</v>
+        <v>136352484</v>
       </c>
       <c r="B65" t="n">
-        <v>79327</v>
+        <v>57198</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kloten, Vstm</t>
+          <t>Södra Kloten, N om, Vstm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>517008</v>
+        <v>516955</v>
       </c>
       <c r="R65" t="n">
-        <v>6633828</v>
+        <v>6634420</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8124,12 +8137,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2019-10-01</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Flög in över vägen framför bilen och blev nästan påkörd.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8140,31 +8158,36 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85567146</t>
+          <t>https://artportalen.se/Sighting/136352484</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136864192</v>
+        <v>72870976</v>
       </c>
       <c r="B66" t="n">
-        <v>104073</v>
+        <v>97986</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8172,16 +8195,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>223284</v>
+        <v>221946</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8190,23 +8213,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Övre Gillermossen, Malingsbo-Klotens naturvårdsområde, Vstm</t>
+          <t>S Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>517293</v>
+        <v>516944</v>
       </c>
       <c r="R66" t="n">
-        <v>6632960</v>
+        <v>6634445</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8230,12 +8249,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8244,75 +8263,77 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Dike</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>grusvägsdike i barrskog</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136864192</t>
+          <t>https://artportalen.se/Sighting/72870976</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>72870974</v>
+        <v>85567146</v>
       </c>
       <c r="B67" t="n">
-        <v>99038</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Skräddarnas, Vstm</t>
+          <t>Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>517322</v>
+        <v>517008</v>
       </c>
       <c r="R67" t="n">
-        <v>6632880</v>
+        <v>6633828</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8339,12 +8360,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8355,40 +8376,31 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72870974</t>
+          <t>https://artportalen.se/Sighting/85567146</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>72870975</v>
+        <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>99038</v>
+        <v>104073</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8396,33 +8408,41 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>223597</v>
+        <v>223284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Skräddarnas, Vstm</t>
+          <t>Övre Gillermossen, Malingsbo-Klotens naturvårdsområde, Vstm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>517560</v>
+        <v>517293</v>
       </c>
       <c r="R68" t="n">
-        <v>6632442</v>
+        <v>6632960</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8446,12 +8466,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2018-07-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8460,88 +8480,75 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Vägkant</t>
+          <t>Dike</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>grusvägsdike i barrskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72870975</t>
+          <t>https://artportalen.se/Sighting/136864192</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>80252484</v>
+        <v>72870974</v>
       </c>
       <c r="B69" t="n">
-        <v>93197</v>
+        <v>99038</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>223597</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Treöresvägen, Vstm</t>
+          <t>Skräddarnas, Vstm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520297</v>
+        <v>517322</v>
       </c>
       <c r="R69" t="n">
-        <v>6632071</v>
+        <v>6632880</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8568,12 +8575,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8582,80 +8589,73 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80252484</t>
+          <t>https://artportalen.se/Sighting/72870974</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>80252535</v>
+        <v>72870975</v>
       </c>
       <c r="B70" t="n">
-        <v>93197</v>
+        <v>99038</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>223597</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Treöresvägen, Vstm</t>
+          <t>Skräddarnas, Vstm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520387</v>
+        <v>517560</v>
       </c>
       <c r="R70" t="n">
-        <v>6631778</v>
+        <v>6632442</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8682,12 +8682,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2019-10-02</t>
+          <t>2018-07-03</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8696,60 +8696,76 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Johan Lilja</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80252535</t>
+          <t>https://artportalen.se/Sighting/72870975</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>80252435</v>
+        <v>80252484</v>
       </c>
       <c r="B71" t="n">
-        <v>91872</v>
+        <v>93197</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
@@ -8758,13 +8774,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520323</v>
+        <v>520297</v>
       </c>
       <c r="R71" t="n">
-        <v>6631763</v>
+        <v>6632071</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8820,38 +8836,38 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80252435</t>
+          <t>https://artportalen.se/Sighting/80252484</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>85567007</v>
+        <v>80252535</v>
       </c>
       <c r="B72" t="n">
-        <v>57141</v>
+        <v>93197</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8859,20 +8875,23 @@
           <t>3</t>
         </is>
       </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kloten, Vstm</t>
+          <t>Treöresvägen, Vstm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520354</v>
+        <v>520387</v>
       </c>
       <c r="R72" t="n">
-        <v>6631282</v>
+        <v>6631778</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8899,12 +8918,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2020-04-15</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2020-04-15</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8913,33 +8932,34 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85567007</t>
+          <t>https://artportalen.se/Sighting/80252535</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122660696</v>
+        <v>80252435</v>
       </c>
       <c r="B73" t="n">
-        <v>56766</v>
+        <v>91872</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8947,44 +8967,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100077</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Nyckelbäcken, Vstm</t>
+          <t>Treöresvägen, Vstm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519239</v>
+        <v>520323</v>
       </c>
       <c r="R73" t="n">
-        <v>6629256</v>
+        <v>6631763</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9011,17 +9024,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2019-08-21</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2019-08-21</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Vägtrumma</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9030,35 +9038,31 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AS73" t="inlineStr">
-        <is>
-          <t>Per Ingvarsson</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Via Henrik Josefsson</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122660696</t>
+          <t>https://artportalen.se/Sighting/80252435</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>93696874</v>
+        <v>85567007</v>
       </c>
       <c r="B74" t="n">
         <v>57141</v>
@@ -9088,37 +9092,26 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>Kloten, Vstm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>522428</v>
+        <v>520354</v>
       </c>
       <c r="R74" t="n">
-        <v>6628384</v>
+        <v>6631282</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9142,22 +9135,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2020-04-15</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2021-05-23</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2020-04-15</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9172,27 +9155,27 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bengt-Ove Lindberg</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bengt-Ove Lindberg</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/93696874</t>
+          <t>https://artportalen.se/Sighting/85567007</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>92859293</v>
+        <v>122660696</v>
       </c>
       <c r="B75" t="n">
-        <v>57144</v>
+        <v>56766</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9200,16 +9183,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>102613</v>
+        <v>100077</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9218,26 +9201,29 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lindesberg, Vstm</t>
+          <t>Nyckelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>522606</v>
+        <v>519239</v>
       </c>
       <c r="R75" t="n">
-        <v>6628180</v>
+        <v>6629256</v>
       </c>
       <c r="S75" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9261,22 +9247,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>08:16</t>
+          <t>2019-08-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2021-04-29</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>08:16</t>
+          <t>2019-08-21</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Vägtrumma</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9287,53 +9268,58 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>Per Ingvarsson</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bengt-Ove Lindberg</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bengt-Ove Lindberg</t>
+          <t>Via Henrik Josefsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92859293</t>
+          <t>https://artportalen.se/Sighting/122660696</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>98536837</v>
+        <v>93696874</v>
       </c>
       <c r="B76" t="n">
-        <v>56816</v>
+        <v>57141</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>205998</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -9341,9 +9327,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>registreringar</t>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -9351,24 +9342,19 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Norrmogen, Vstm</t>
+          <t>Lindesberg, Vstm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>522653</v>
+        <v>522428</v>
       </c>
       <c r="R76" t="n">
-        <v>6628363</v>
+        <v>6628384</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9392,22 +9378,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>00:47</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
+          <t>2021-05-23</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>00:47</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9422,84 +9408,72 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Bengt-Ove Lindberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Bengt-Ove Lindberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536837</t>
+          <t>https://artportalen.se/Sighting/93696874</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>98536839</v>
+        <v>92859293</v>
       </c>
       <c r="B77" t="n">
-        <v>56816</v>
+        <v>57144</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>205998</v>
+        <v>102613</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrmogen, Vstm</t>
+          <t>Lindesberg, Vstm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>522680</v>
+        <v>522606</v>
       </c>
       <c r="R77" t="n">
-        <v>6628361</v>
+        <v>6628180</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9523,22 +9497,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>00:47</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2021-07-25</t>
+          <t>2021-04-29</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>00:47</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9553,24 +9527,24 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Bengt-Ove Lindberg</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Bengt-Ove Lindberg</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536839</t>
+          <t>https://artportalen.se/Sighting/92859293</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>98536862</v>
+        <v>98536837</v>
       </c>
       <c r="B78" t="n">
         <v>56816</v>
@@ -9624,10 +9598,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>522163</v>
+        <v>522653</v>
       </c>
       <c r="R78" t="n">
-        <v>6628351</v>
+        <v>6628363</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9654,22 +9628,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>23:46</t>
+          <t>00:47</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-07-25</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>23:46</t>
+          <t>00:47</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9695,13 +9669,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536862</t>
+          <t>https://artportalen.se/Sighting/98536837</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>98536863</v>
+        <v>98536839</v>
       </c>
       <c r="B79" t="n">
         <v>56816</v>
@@ -9755,10 +9729,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>522878</v>
+        <v>522680</v>
       </c>
       <c r="R79" t="n">
-        <v>6628396</v>
+        <v>6628361</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9785,22 +9759,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>23:44</t>
+          <t>00:47</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
+          <t>2021-07-25</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>23:44</t>
+          <t>00:47</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9826,13 +9800,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536863</t>
+          <t>https://artportalen.se/Sighting/98536839</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>98536882</v>
+        <v>98536862</v>
       </c>
       <c r="B80" t="n">
         <v>56816</v>
@@ -9886,10 +9860,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>522384</v>
+        <v>522163</v>
       </c>
       <c r="R80" t="n">
-        <v>6628361</v>
+        <v>6628351</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9916,22 +9890,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
+          <t>2021-07-23</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>23:46</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9957,13 +9931,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536882</t>
+          <t>https://artportalen.se/Sighting/98536862</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>98536883</v>
+        <v>98536863</v>
       </c>
       <c r="B81" t="n">
         <v>56816</v>
@@ -10017,10 +9991,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>522735</v>
+        <v>522878</v>
       </c>
       <c r="R81" t="n">
-        <v>6628361</v>
+        <v>6628396</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10047,22 +10021,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2021-07-21</t>
+          <t>2021-07-23</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>23:44</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-07-24</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>23:54</t>
+          <t>23:44</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10088,13 +10062,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536883</t>
+          <t>https://artportalen.se/Sighting/98536863</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>98536884</v>
+        <v>98536882</v>
       </c>
       <c r="B82" t="n">
         <v>56816</v>
@@ -10148,10 +10122,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>522777</v>
+        <v>522384</v>
       </c>
       <c r="R82" t="n">
-        <v>6628381</v>
+        <v>6628361</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10183,7 +10157,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>23:55</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10193,7 +10167,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>23:55</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10219,13 +10193,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536884</t>
+          <t>https://artportalen.se/Sighting/98536882</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>98536885</v>
+        <v>98536883</v>
       </c>
       <c r="B83" t="n">
         <v>56816</v>
@@ -10279,10 +10253,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>522788</v>
+        <v>522735</v>
       </c>
       <c r="R83" t="n">
-        <v>6628388</v>
+        <v>6628361</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10314,7 +10288,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10324,7 +10298,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>23:54</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10350,13 +10324,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536885</t>
+          <t>https://artportalen.se/Sighting/98536883</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>98536886</v>
+        <v>98536884</v>
       </c>
       <c r="B84" t="n">
         <v>56816</v>
@@ -10410,10 +10384,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>522804</v>
+        <v>522777</v>
       </c>
       <c r="R84" t="n">
-        <v>6628394</v>
+        <v>6628381</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10481,16 +10455,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536886</t>
+          <t>https://artportalen.se/Sighting/98536884</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>95457108</v>
+        <v>98536885</v>
       </c>
       <c r="B85" t="n">
-        <v>93215</v>
+        <v>56816</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10498,40 +10472,56 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4368</v>
+        <v>205998</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Ormpussen, Vstm</t>
+          <t>Norrmogen, Vstm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523487</v>
+        <v>522788</v>
       </c>
       <c r="R85" t="n">
-        <v>6628132</v>
+        <v>6628388</v>
       </c>
       <c r="S85" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10555,12 +10545,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2021-07-21</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10569,72 +10569,90 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Linn Svensson</t>
+          <t>Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95457108</t>
+          <t>https://artportalen.se/Sighting/98536885</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>98351190</v>
+        <v>98536886</v>
       </c>
       <c r="B86" t="n">
-        <v>97986</v>
+        <v>56816</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221946</v>
+        <v>205998</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>BatLogger</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gammelbo, Vstm</t>
+          <t>Norrmogen, Vstm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523565</v>
+        <v>522804</v>
       </c>
       <c r="R86" t="n">
-        <v>6627791</v>
+        <v>6628394</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10658,12 +10676,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-07-21</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2021-05-08</t>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>23:53</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10678,31 +10706,27 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t>Miniforskningsresan Extensus Örebro län 2021</t>
-        </is>
-      </c>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98351190</t>
+          <t>https://artportalen.se/Sighting/98536886</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>98536876</v>
+        <v>95457108</v>
       </c>
       <c r="B87" t="n">
-        <v>56816</v>
+        <v>93215</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10710,56 +10734,40 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>205998</v>
+        <v>4368</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>BatLogger</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norrmogen, Vstm</t>
+          <t>Ormpussen, Vstm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>525086</v>
+        <v>523487</v>
       </c>
       <c r="R87" t="n">
-        <v>6628007</v>
+        <v>6628132</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10783,22 +10791,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>00:16</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>00:16</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10807,90 +10805,72 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Linn Svensson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536876</t>
+          <t>https://artportalen.se/Sighting/95457108</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>98537195</v>
+        <v>98351190</v>
       </c>
       <c r="B88" t="n">
-        <v>56814</v>
+        <v>97986</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100015</v>
+        <v>221946</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norrmogen, Vstm</t>
+          <t>Gammelbo, Vstm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>525810</v>
+        <v>523565</v>
       </c>
       <c r="R88" t="n">
-        <v>6627350</v>
+        <v>6627791</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10914,22 +10894,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>21:30</t>
+          <t>2021-05-08</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>05:00</t>
+          <t>2021-05-08</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10940,63 +10910,62 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AS88" t="inlineStr">
-        <is>
-          <t>Johnny de Jong</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98537195</t>
+          <t>https://artportalen.se/Sighting/98351190</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>98536579</v>
+        <v>98536876</v>
       </c>
       <c r="B89" t="n">
-        <v>56823</v>
+        <v>56816</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11011,7 +10980,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>autobox med tidsexpansion</t>
+          <t>BatLogger</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11020,10 +10989,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>525810</v>
+        <v>525086</v>
       </c>
       <c r="R89" t="n">
-        <v>6627350</v>
+        <v>6628007</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -11050,22 +11019,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
+          <t>2021-07-22</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>00:16</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
           <t>2021-07-23</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2021-07-24</t>
-        </is>
-      </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11076,11 +11045,6 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AS89" t="inlineStr">
-        <is>
-          <t>Johnny de Jong</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11096,16 +11060,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536579</t>
+          <t>https://artportalen.se/Sighting/98536876</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>98536910</v>
+        <v>98537195</v>
       </c>
       <c r="B90" t="n">
-        <v>56816</v>
+        <v>56814</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11113,26 +11077,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>205998</v>
+        <v>100015</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11232,43 +11196,43 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98536910</t>
+          <t>https://artportalen.se/Sighting/98537195</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>98535806</v>
+        <v>98536579</v>
       </c>
       <c r="B91" t="n">
-        <v>56837</v>
+        <v>56823</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>206002</v>
+        <v>205992</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11368,16 +11332,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98535806</t>
+          <t>https://artportalen.se/Sighting/98536579</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124825217</v>
+        <v>98536910</v>
       </c>
       <c r="B92" t="n">
-        <v>93197</v>
+        <v>56816</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11385,38 +11349,53 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>205998</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Norrmogen, Vstm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>498767</v>
+        <v>525810</v>
       </c>
       <c r="R92" t="n">
-        <v>6626190</v>
+        <v>6627350</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -11438,22 +11417,27 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Ramsberg</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11464,31 +11448,36 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>Johnny de Jong</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825217</t>
+          <t>https://artportalen.se/Sighting/98536910</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124825221</v>
+        <v>98535806</v>
       </c>
       <c r="B93" t="n">
-        <v>93197</v>
+        <v>56837</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11496,38 +11485,53 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>206002</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Norrmogen, Vstm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>498811</v>
+        <v>525810</v>
       </c>
       <c r="R93" t="n">
-        <v>6626221</v>
+        <v>6627350</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11549,22 +11553,27 @@
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>Ramsberg</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>2021-07-24</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11575,74 +11584,75 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>Johnny de Jong</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Martin Brüsin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Alexander Eriksson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825221</t>
+          <t>https://artportalen.se/Sighting/98535806</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124825220</v>
+        <v>124825217</v>
       </c>
       <c r="B94" t="n">
-        <v>57141</v>
+        <v>93197</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>498810</v>
+        <v>498767</v>
       </c>
       <c r="R94" t="n">
-        <v>6626227</v>
+        <v>6626190</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11705,55 +11715,43 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825220</t>
+          <t>https://artportalen.se/Sighting/124825217</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124825285</v>
+        <v>124825221</v>
       </c>
       <c r="B95" t="n">
-        <v>57141</v>
+        <v>93197</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11762,13 +11760,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>498809</v>
+        <v>498811</v>
       </c>
       <c r="R95" t="n">
-        <v>6626228</v>
+        <v>6626221</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11802,7 +11800,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.Synobs. Tupp</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11828,16 +11826,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825285</t>
+          <t>https://artportalen.se/Sighting/124825221</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124825211</v>
+        <v>124825220</v>
       </c>
       <c r="B96" t="n">
-        <v>5179</v>
+        <v>57141</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11845,21 +11843,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11867,16 +11865,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>498899</v>
+        <v>498810</v>
       </c>
       <c r="R96" t="n">
-        <v>6625787</v>
+        <v>6626227</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11939,16 +11941,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825211</t>
+          <t>https://artportalen.se/Sighting/124825220</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124825214</v>
+        <v>124825285</v>
       </c>
       <c r="B97" t="n">
-        <v>5179</v>
+        <v>57141</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11956,26 +11958,38 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11984,13 +11998,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>499066</v>
+        <v>498809</v>
       </c>
       <c r="R97" t="n">
-        <v>6626115</v>
+        <v>6626228</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12024,7 +12038,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.Synobs. Tupp</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12050,13 +12064,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825214</t>
+          <t>https://artportalen.se/Sighting/124825285</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124825290</v>
+        <v>124825211</v>
       </c>
       <c r="B98" t="n">
         <v>5179</v>
@@ -12095,13 +12109,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>498898</v>
+        <v>498899</v>
       </c>
       <c r="R98" t="n">
-        <v>6625781</v>
+        <v>6625787</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12161,16 +12175,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825290</t>
+          <t>https://artportalen.se/Sighting/124825211</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124825216</v>
+        <v>124825214</v>
       </c>
       <c r="B99" t="n">
-        <v>99035</v>
+        <v>5179</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12178,26 +12192,26 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219790</v>
+        <v>100526</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12206,10 +12220,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>498747</v>
+        <v>499066</v>
       </c>
       <c r="R99" t="n">
-        <v>6625877</v>
+        <v>6626115</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -12272,16 +12286,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124825216</t>
+          <t>https://artportalen.se/Sighting/124825214</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>66418932</v>
+        <v>124825290</v>
       </c>
       <c r="B100" t="n">
-        <v>99036</v>
+        <v>5179</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12289,44 +12303,41 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>223591</v>
+        <v>100526</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Strävtorp, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>496339</v>
+        <v>498898</v>
       </c>
       <c r="R100" t="n">
-        <v>6624902</v>
+        <v>6625781</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12350,22 +12361,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2017-06-23</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2017-06-23</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12380,65 +12386,69 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Bengt Adamsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Bengt Adamsson , Bodil Nyström, Conny Palm, Stig Carlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66418932</t>
+          <t>https://artportalen.se/Sighting/124825290</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>122230880</v>
+        <v>124825216</v>
       </c>
       <c r="B101" t="n">
-        <v>79327</v>
+        <v>99035</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Rasbacktjärn, Vstm</t>
+          <t>Gullblanka, Vstm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>495350</v>
+        <v>498747</v>
       </c>
       <c r="R101" t="n">
-        <v>6624698</v>
+        <v>6625877</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12462,12 +12472,17 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2025-04-29</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12482,27 +12497,27 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122230880</t>
+          <t>https://artportalen.se/Sighting/124825216</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>122230857</v>
+        <v>66418932</v>
       </c>
       <c r="B102" t="n">
-        <v>80467</v>
+        <v>99036</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12510,34 +12525,41 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6463</v>
+        <v>223591</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Rasbacktjärn, Vstm</t>
+          <t>Strävtorp, Vstm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>495356</v>
+        <v>496339</v>
       </c>
       <c r="R102" t="n">
-        <v>6624327</v>
+        <v>6624902</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12564,12 +12586,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2017-06-23</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2017-06-23</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12584,70 +12616,62 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Bengt Adamsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Bengt Adamsson , Bodil Nyström, Conny Palm, Stig Carlsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122230857</t>
+          <t>https://artportalen.se/Sighting/66418932</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>122230848</v>
+        <v>122230880</v>
       </c>
       <c r="B103" t="n">
-        <v>57141</v>
+        <v>79327</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rasbacktjärn, Vstm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>495309</v>
+        <v>495350</v>
       </c>
       <c r="R103" t="n">
-        <v>6624438</v>
+        <v>6624698</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12674,12 +12698,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-12-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12705,55 +12729,51 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122230848</t>
+          <t>https://artportalen.se/Sighting/122230880</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>122230856</v>
+        <v>122230857</v>
       </c>
       <c r="B104" t="n">
-        <v>58114</v>
+        <v>80467</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rasbacktjärn, Vstm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>495359</v>
+        <v>495356</v>
       </c>
       <c r="R104" t="n">
-        <v>6624369</v>
+        <v>6624327</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -12811,16 +12831,16 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122230856</t>
+          <t>https://artportalen.se/Sighting/122230857</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>82883664</v>
+        <v>122230848</v>
       </c>
       <c r="B105" t="n">
-        <v>96554</v>
+        <v>57141</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12828,34 +12848,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Hammarskogsån, Vstm</t>
+          <t>Rasbacktjärn, Vstm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>503753</v>
+        <v>495309</v>
       </c>
       <c r="R105" t="n">
-        <v>6624241</v>
+        <v>6624438</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -12882,12 +12910,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12898,80 +12926,70 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>Barrskog i litet dalstråk</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883664</t>
+          <t>https://artportalen.se/Sighting/122230848</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>82883685</v>
+        <v>122230856</v>
       </c>
       <c r="B106" t="n">
-        <v>97989</v>
+        <v>58114</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Hammarskogsån, Vstm</t>
+          <t>Rasbacktjärn, Vstm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>504568</v>
+        <v>495359</v>
       </c>
       <c r="R106" t="n">
-        <v>6623836</v>
+        <v>6624369</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12998,12 +13016,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13014,40 +13032,31 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>Tallbestånd</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Per Ahlqvist</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883685</t>
+          <t>https://artportalen.se/Sighting/122230856</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135456621</v>
+        <v>82883664</v>
       </c>
       <c r="B107" t="n">
-        <v>57783</v>
+        <v>96554</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13055,49 +13064,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>102118</v>
+        <v>210</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Midtjärnsviken, Vstm</t>
+          <t>Hammarskogsån, Vstm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>500203</v>
+        <v>503753</v>
       </c>
       <c r="R107" t="n">
-        <v>6623603</v>
+        <v>6624241</v>
       </c>
       <c r="S107" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13121,27 +13118,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>22:35</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>22:42</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Även lockläte hörs några ggr.</t>
+          <t>2018-10-03</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13152,31 +13134,45 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Barrskog i litet dalstråk</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Fredrik Johansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Fredrik Johansson</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135456621</t>
+          <t>https://artportalen.se/Sighting/82883664</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>82883645</v>
+        <v>82883685</v>
       </c>
       <c r="B108" t="n">
-        <v>97678</v>
+        <v>97989</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13184,21 +13180,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2326</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13208,10 +13204,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>503428</v>
+        <v>504568</v>
       </c>
       <c r="R108" t="n">
-        <v>6623052</v>
+        <v>6623836</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -13257,12 +13253,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>Sumpdråg</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Murken ved av lövträd</t>
+          <t>Tallbestånd</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13283,16 +13274,16 @@
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883645</t>
+          <t>https://artportalen.se/Sighting/82883685</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>82883638</v>
+        <v>135456621</v>
       </c>
       <c r="B109" t="n">
-        <v>97780</v>
+        <v>57783</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13300,37 +13291,49 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2389</v>
+        <v>102118</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Purpurmylia</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Mylia taylorii</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hook.) Gray</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Hammarskogsån, Vstm</t>
+          <t>Midtjärnsviken, Vstm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>503461</v>
+        <v>500203</v>
       </c>
       <c r="R109" t="n">
-        <v>6623044</v>
+        <v>6623603</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13354,12 +13357,27 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2018-10-03</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>22:42</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Även lockläte hörs några ggr.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13370,45 +13388,31 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Blocksida</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Henrik Josefsson</t>
+          <t>Fredrik Johansson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Fredrik Johansson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883638</t>
+          <t>https://artportalen.se/Sighting/135456621</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>82883606</v>
+        <v>82883645</v>
       </c>
       <c r="B110" t="n">
-        <v>97231</v>
+        <v>97678</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13416,21 +13420,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2869</v>
+        <v>2326</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13440,10 +13444,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>503469</v>
+        <v>503428</v>
       </c>
       <c r="R110" t="n">
-        <v>6623043</v>
+        <v>6623052</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -13489,7 +13493,12 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Sumpdråg</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Murken ved av lövträd</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -13510,38 +13519,38 @@
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883606</t>
+          <t>https://artportalen.se/Sighting/82883645</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>82883551</v>
+        <v>82883638</v>
       </c>
       <c r="B111" t="n">
-        <v>93215</v>
+        <v>97780</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4368</v>
+        <v>2389</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Purpurmylia</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Mylia taylorii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Hook.) Gray</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13551,10 +13560,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>501532</v>
+        <v>503461</v>
       </c>
       <c r="R111" t="n">
-        <v>6622785</v>
+        <v>6623044</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -13600,7 +13609,12 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>Örtgranskog vid å</t>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Blocksida</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -13621,54 +13635,54 @@
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82883551</t>
+          <t>https://artportalen.se/Sighting/82883638</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>89825681</v>
+        <v>82883606</v>
       </c>
       <c r="B112" t="n">
-        <v>93215</v>
+        <v>97231</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4368</v>
+        <v>2869</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Hammarbäcken, Vstm</t>
+          <t>Hammarskogsån, Vstm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>501528</v>
+        <v>503469</v>
       </c>
       <c r="R112" t="n">
-        <v>6622791</v>
+        <v>6623043</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13692,12 +13706,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2018-08-23</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2018-10-03</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13711,31 +13725,253 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>Åstrand med lövrik blandskog</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Äldre granbestånd</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883606</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>82883551</v>
+      </c>
+      <c r="B113" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Hammarskogsån, Vstm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>501532</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6622785</v>
+      </c>
+      <c r="S113" t="n">
+        <v>25</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2018-08-23</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2018-10-03</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Örtgranskog vid å</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82883551</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>89825681</v>
+      </c>
+      <c r="B114" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Hammarbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>501528</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6622791</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2020-10-22</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2020-10-22</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>Åstrand med lövrik blandskog</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Äldre granbestånd</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
           <t>Henrik Weibull</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
+      <c r="AX114" t="inlineStr">
         <is>
           <t>Henrik Weibull</t>
         </is>
       </c>
-      <c r="AY112" t="inlineStr">
+      <c r="AY114" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
+      <c r="AZ114" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/89825681</t>
         </is>
@@ -13854,6 +14090,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7362,7 +7362,7 @@
         <v>136352545</v>
       </c>
       <c r="B59" t="n">
-        <v>106528</v>
+        <v>106534</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136352621</v>
       </c>
       <c r="B60" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>136352540</v>
       </c>
       <c r="B61" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>136352542</v>
       </c>
       <c r="B62" t="n">
-        <v>98404</v>
+        <v>98410</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106528</v>
+        <v>106534</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104073</v>
+        <v>104079</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7362,7 +7362,7 @@
         <v>136352545</v>
       </c>
       <c r="B59" t="n">
-        <v>106534</v>
+        <v>106536</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>136352621</v>
       </c>
       <c r="B60" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>136352540</v>
       </c>
       <c r="B61" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>136352542</v>
       </c>
       <c r="B62" t="n">
-        <v>98410</v>
+        <v>98412</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106534</v>
+        <v>106536</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104079</v>
+        <v>104081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106536</v>
+        <v>106537</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104081</v>
+        <v>104082</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106537</v>
+        <v>106543</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104082</v>
+        <v>104088</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106543</v>
+        <v>106547</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104088</v>
+        <v>104092</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106547</v>
+        <v>106549</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104092</v>
+        <v>104094</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106549</v>
+        <v>106551</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104094</v>
+        <v>104096</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106551</v>
+        <v>106564</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104096</v>
+        <v>104109</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106564</v>
+        <v>106566</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104109</v>
+        <v>104111</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7842,11 +7842,7 @@
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106566</v>
+        <v>106570</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104111</v>
+        <v>104114</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106570</v>
+        <v>106590</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104114</v>
+        <v>104129</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106590</v>
+        <v>106591</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104129</v>
+        <v>104130</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106591</v>
+        <v>106596</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104130</v>
+        <v>104135</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106596</v>
+        <v>106599</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104135</v>
+        <v>104138</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106599</v>
+        <v>106605</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104138</v>
+        <v>104144</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106605</v>
+        <v>106606</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104144</v>
+        <v>104145</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106606</v>
+        <v>106618</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>136864192</v>
       </c>
       <c r="B68" t="n">
-        <v>104145</v>
+        <v>104157</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106618</v>
+        <v>106619</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106619</v>
+        <v>106622</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106622</v>
+        <v>106624</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/S 3568-2025 artfynd.xlsx
+++ b/artfynd/S 3568-2025 artfynd.xlsx
@@ -7815,7 +7815,7 @@
         <v>136941249</v>
       </c>
       <c r="B63" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>136941079</v>
       </c>
       <c r="B64" t="n">
-        <v>106624</v>
+        <v>106628</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
